--- a/master/result/16_仙途问道：青云之路/16_仙途问道.xlsx
+++ b/master/result/16_仙途问道：青云之路/16_仙途问道.xlsx
@@ -397,577 +397,731 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>northeast</v>
       </c>
       <c r="B2" t="str">
-        <v>northeast</v>
+        <v>/northeast/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>东北</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>neighborhood</v>
       </c>
       <c r="B3" t="str">
-        <v>neighborhood</v>
+        <v>/neighborhood/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>四邻</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>domestic</v>
       </c>
       <c r="B4" t="str">
-        <v>domestic</v>
+        <v>/domestic/</v>
       </c>
       <c r="C4" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>本国的</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>native</v>
       </c>
       <c r="B5" t="str">
-        <v>native</v>
+        <v>/native/</v>
       </c>
       <c r="C5" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>本地的</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>uncle</v>
       </c>
       <c r="B6" t="str">
-        <v>uncle</v>
+        <v>/uncle/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>叔父</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>October</v>
       </c>
       <c r="B7" t="str">
-        <v>October</v>
+        <v>/October/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>十月</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>originate</v>
       </c>
       <c r="B8" t="str">
-        <v>originate</v>
+        <v>/originate/</v>
       </c>
       <c r="C8" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D8" t="str">
         <v>起源</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>dead</v>
       </c>
       <c r="B9" t="str">
-        <v>dead</v>
+        <v>/dead/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>死的</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>barbecue</v>
       </c>
       <c r="B10" t="str">
-        <v>barbecue</v>
+        <v>/barbecue/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>烤肉</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>mutton</v>
       </c>
       <c r="B11" t="str">
-        <v>mutton</v>
+        <v>/mutton/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>羊肉</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>protein</v>
       </c>
       <c r="B12" t="str">
-        <v>protein</v>
+        <v>/protein/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>蛋白质</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>type</v>
       </c>
       <c r="B13" t="str">
-        <v>type</v>
+        <v>/taɪp/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>类型</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>energy</v>
       </c>
       <c r="B14" t="str">
-        <v>energy</v>
+        <v>/energy/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>能量</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>swell</v>
       </c>
       <c r="B15" t="str">
-        <v>swell</v>
+        <v>/swell/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>膨胀</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>pine</v>
       </c>
       <c r="B16" t="str">
-        <v>pine</v>
+        <v>/pine/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>松树</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>melody</v>
       </c>
       <c r="B17" t="str">
-        <v>melody</v>
+        <v>/melody/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>旋律</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>comprehensive</v>
       </c>
       <c r="B18" t="str">
-        <v>comprehensive</v>
+        <v>/comprehensive/</v>
       </c>
       <c r="C18" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D18" t="str">
         <v>综合</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>passive</v>
       </c>
       <c r="B19" t="str">
-        <v>passive</v>
+        <v>/passive/</v>
       </c>
       <c r="C19" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>被动的</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>gradual</v>
       </c>
       <c r="B20" t="str">
-        <v>gradual</v>
+        <v>/gradual/</v>
       </c>
       <c r="C20" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>逐渐</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>measure</v>
       </c>
       <c r="B21" t="str">
-        <v>measure</v>
+        <v>/ˈmeʒə/</v>
       </c>
       <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>测量</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>method</v>
       </c>
       <c r="B22" t="str">
-        <v>method</v>
+        <v>/method/</v>
       </c>
       <c r="C22" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>方法</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>crown</v>
       </c>
       <c r="B23" t="str">
-        <v>crown</v>
+        <v>/kraʊn/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>加冕</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>external</v>
       </c>
       <c r="B24" t="str">
-        <v>external</v>
+        <v>/external/</v>
       </c>
       <c r="C24" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D24" t="str">
         <v>外部</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>theater</v>
       </c>
       <c r="B25" t="str">
-        <v>theater</v>
+        <v>/theater/</v>
       </c>
       <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
         <v>戏院</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>ban</v>
       </c>
       <c r="B26" t="str">
-        <v>ban</v>
+        <v>/bæn/</v>
       </c>
       <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>禁止</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>prepare</v>
       </c>
       <c r="B27" t="str">
-        <v>prepare</v>
+        <v>/prɪˈpeə/</v>
       </c>
       <c r="C27" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>准备</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>infer</v>
       </c>
       <c r="B28" t="str">
-        <v>infer</v>
+        <v>/infer/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>推断</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>universal</v>
       </c>
       <c r="B29" t="str">
-        <v>universal</v>
+        <v>/universal/</v>
       </c>
       <c r="C29" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D29" t="str">
         <v>普遍</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>monitor</v>
       </c>
       <c r="B30" t="str">
-        <v>monitor</v>
+        <v>/monitor/</v>
       </c>
       <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>监视</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>presumably</v>
       </c>
       <c r="B31" t="str">
-        <v>presumably</v>
+        <v>/presumably/</v>
       </c>
       <c r="C31" t="str">
+        <v>adv.</v>
+      </c>
+      <c r="D31" t="str">
         <v>推测起来</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>trick</v>
       </c>
       <c r="B32" t="str">
-        <v>trick</v>
+        <v>/trɪk/</v>
       </c>
       <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>诡计</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>container</v>
       </c>
       <c r="B33" t="str">
-        <v>container</v>
+        <v>/kənˈteɪnə/</v>
       </c>
       <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>容器</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>engagement</v>
       </c>
       <c r="B34" t="str">
-        <v>engagement</v>
+        <v>/engagement/</v>
       </c>
       <c r="C34" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>婚约</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>witch</v>
       </c>
       <c r="B35" t="str">
-        <v>witch</v>
+        <v>/witch/</v>
       </c>
       <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>女巫</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>contradict</v>
       </c>
       <c r="B36" t="str">
-        <v>contradict</v>
+        <v>/contradict/</v>
       </c>
       <c r="C36" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>反驳</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>access</v>
       </c>
       <c r="B37" t="str">
-        <v>access</v>
+        <v>/access/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>进入</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>requirement</v>
       </c>
       <c r="B38" t="str">
-        <v>requirement</v>
+        <v>/requirement/</v>
       </c>
       <c r="C38" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D38" t="str">
         <v>要求</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>adjacent</v>
       </c>
       <c r="B39" t="str">
-        <v>adjacent</v>
+        <v>/adjacent/</v>
       </c>
       <c r="C39" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D39" t="str">
         <v>邻近的</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>straightforward</v>
       </c>
       <c r="B40" t="str">
-        <v>straightforward</v>
+        <v>/straightforward/</v>
       </c>
       <c r="C40" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D40" t="str">
         <v>正直</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>hatch</v>
       </c>
       <c r="B41" t="str">
-        <v>hatch</v>
+        <v>/hatch/</v>
       </c>
       <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
         <v>舱口</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>inspect</v>
       </c>
       <c r="B42" t="str">
-        <v>inspect</v>
+        <v>/inspect/</v>
       </c>
       <c r="C42" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D42" t="str">
         <v>检查</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>substance</v>
       </c>
       <c r="B43" t="str">
-        <v>substance</v>
+        <v>/substance/</v>
       </c>
       <c r="C43" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D43" t="str">
         <v>物质</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>navy</v>
       </c>
       <c r="B44" t="str">
-        <v>navy</v>
+        <v>/navy/</v>
       </c>
       <c r="C44" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D44" t="str">
         <v>海军</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>expenditure</v>
       </c>
       <c r="B45" t="str">
-        <v>expenditure</v>
+        <v>/expenditure/</v>
       </c>
       <c r="C45" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D45" t="str">
         <v>花费</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>ear</v>
       </c>
       <c r="B46" t="str">
-        <v>ear</v>
+        <v>/ear/</v>
       </c>
       <c r="C46" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D46" t="str">
         <v>耳朵</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>counter</v>
       </c>
       <c r="B47" t="str">
-        <v>counter</v>
+        <v>/ˈkaʊntə/</v>
       </c>
       <c r="C47" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D47" t="str">
         <v>反击</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>decent</v>
       </c>
       <c r="B48" t="str">
-        <v>decent</v>
+        <v>/decent/</v>
       </c>
       <c r="C48" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D48" t="str">
         <v>体面的</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>aggravate</v>
       </c>
       <c r="B49" t="str">
-        <v>aggravate</v>
+        <v>/aggravate/</v>
       </c>
       <c r="C49" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D49" t="str">
         <v>加重</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>like</v>
       </c>
       <c r="B50" t="str">
-        <v>like</v>
+        <v>/laɪk/</v>
       </c>
       <c r="C50" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D50" t="str">
         <v>喜欢</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>beg</v>
       </c>
       <c r="B51" t="str">
-        <v>beg</v>
+        <v>/beɡ/</v>
       </c>
       <c r="C51" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D51" t="str">
         <v>请求</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>